--- a/tools/excel-config/level.xlsx
+++ b/tools/excel-config/level.xlsx
@@ -655,7 +655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -667,12 +667,10 @@
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
-    <col width="27" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="27" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -723,30 +721,20 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>rowSpawnInterval</t>
+          <t>spawnStagger</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>bandSpawnInterval</t>
+          <t>fallSpeed</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>spawnStagger</t>
+          <t>isBossWave</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>fallSpeed</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>isBossWave</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
@@ -810,20 +798,10 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>bool</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -877,30 +855,20 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>行入场间隔 秒</t>
+          <t>带内错峰 秒（做出逐个弹出）</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>带入场间隔 秒</t>
+          <t>覆盖默认下移速度 px/s（0 = 用难度曲线）</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>带内错峰 秒（做出逐个弹出）</t>
+          <t>是否 BOSS 波</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>覆盖默认下移速度 px/s（0 = 用难度曲线）</t>
-        </is>
-      </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>是否 BOSS 波</t>
-        </is>
-      </c>
-      <c r="O3" s="3" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -945,21 +913,15 @@
         </is>
       </c>
       <c r="J4" s="4" t="n">
-        <v>0.5</v>
+        <v>0.08</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L4" s="4" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="M4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O4" s="4" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="L4" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
         <is>
           <t>手写：见 Row 表</t>
         </is>
@@ -1004,21 +966,15 @@
         </is>
       </c>
       <c r="J5" s="4" t="n">
-        <v>0.5</v>
+        <v>0.08</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L5" s="4" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="M5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O5" s="4" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="L5" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="M5" s="4" t="inlineStr">
         <is>
           <t>手写：引入精英</t>
         </is>
@@ -1063,21 +1019,15 @@
         </is>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.5</v>
+        <v>0.08</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L6" s="4" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="M6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O6" s="4" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="L6" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
         <is>
           <t>随机：2 个带 = 4 行</t>
         </is>
@@ -1122,21 +1072,15 @@
         </is>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.5</v>
+        <v>0.08</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L7" s="4" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="M7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="O7" s="4" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="L7" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="M7" s="4" t="inlineStr">
         <is>
           <t>手写 BOSS 波：四格小BOSS</t>
         </is>
@@ -1181,21 +1125,15 @@
         </is>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.5</v>
+        <v>0.08</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L8" s="4" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="M8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O8" s="4" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="L8" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="M8" s="4" t="inlineStr">
         <is>
           <t>教学期：只有白绿</t>
         </is>
@@ -1240,21 +1178,15 @@
         </is>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.5</v>
+        <v>0.08</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L9" s="4" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="M9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O9" s="4" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="L9" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="M9" s="4" t="inlineStr">
         <is>
           <t>引入蓝与少量紫</t>
         </is>
@@ -1299,21 +1231,15 @@
         </is>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.5</v>
+        <v>0.08</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L10" s="4" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="M10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O10" s="4" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="L10" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="M10" s="4" t="inlineStr">
         <is>
           <t>攻击型占比上升（§8.5）</t>
         </is>
@@ -1358,21 +1284,15 @@
         </is>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.5</v>
+        <v>0.08</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L11" s="4" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="M11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O11" s="4" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="L11" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="M11" s="4" t="inlineStr">
         <is>
           <t>全品质开放</t>
         </is>
@@ -1383,7 +1303,7 @@
     <dataValidation sqref="D4:D300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="枚举取值非法" error="取值必须在：0,1" type="list">
       <formula1>"0,1"</formula1>
     </dataValidation>
-    <dataValidation sqref="N4:N300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="枚举取值非法" error="取值必须在：TRUE,FALSE" type="list">
+    <dataValidation sqref="L4:L300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="枚举取值非法" error="取值必须在：TRUE,FALSE" type="list">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
   </dataValidations>
